--- a/artfynd/A 26484-2025 artfynd.xlsx
+++ b/artfynd/A 26484-2025 artfynd.xlsx
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126055042</v>
+        <v>126055038</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>98355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745337</v>
+        <v>745343</v>
       </c>
       <c r="R8" t="n">
-        <v>7103251</v>
+        <v>7103338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1332,17 +1332,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126055038</v>
+        <v>126055042</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745343</v>
+        <v>745337</v>
       </c>
       <c r="R9" t="n">
-        <v>7103338</v>
+        <v>7103251</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,12 +1429,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26484-2025 artfynd.xlsx
+++ b/artfynd/A 26484-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126055046</v>
       </c>
       <c r="B2" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126055035</v>
       </c>
       <c r="B3" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126055041</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126055045</v>
       </c>
       <c r="B5" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126055043</v>
       </c>
       <c r="B6" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126055037</v>
+        <v>126055042</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745308</v>
+        <v>745337</v>
       </c>
       <c r="R7" t="n">
-        <v>7103303</v>
+        <v>7103251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126055038</v>
+        <v>126055037</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745343</v>
+        <v>745308</v>
       </c>
       <c r="R8" t="n">
-        <v>7103338</v>
+        <v>7103303</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1332,12 +1337,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126055042</v>
+        <v>126055038</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>98359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745337</v>
+        <v>745343</v>
       </c>
       <c r="R9" t="n">
-        <v>7103251</v>
+        <v>7103338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1429,17 +1434,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26484-2025 artfynd.xlsx
+++ b/artfynd/A 26484-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126055046</v>
       </c>
       <c r="B2" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126055045</v>
       </c>
       <c r="B5" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126055043</v>
       </c>
       <c r="B6" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>126055037</v>
       </c>
       <c r="B8" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>126055038</v>
       </c>
       <c r="B9" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26484-2025 artfynd.xlsx
+++ b/artfynd/A 26484-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126055046</v>
       </c>
       <c r="B2" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126055035</v>
       </c>
       <c r="B3" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126055041</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126055045</v>
       </c>
       <c r="B5" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126055043</v>
       </c>
       <c r="B6" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126055042</v>
+        <v>126055037</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>98362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745337</v>
+        <v>745308</v>
       </c>
       <c r="R7" t="n">
-        <v>7103251</v>
+        <v>7103303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126055037</v>
+        <v>126055038</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745308</v>
+        <v>745343</v>
       </c>
       <c r="R8" t="n">
-        <v>7103303</v>
+        <v>7103338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,12 +1332,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126055038</v>
+        <v>126055042</v>
       </c>
       <c r="B9" t="n">
-        <v>98360</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745343</v>
+        <v>745337</v>
       </c>
       <c r="R9" t="n">
-        <v>7103338</v>
+        <v>7103251</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,12 +1429,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26484-2025 artfynd.xlsx
+++ b/artfynd/A 26484-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126055046</v>
       </c>
       <c r="B2" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126055035</v>
       </c>
       <c r="B3" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126055045</v>
       </c>
       <c r="B5" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126055043</v>
       </c>
       <c r="B6" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126055037</v>
+        <v>126055042</v>
       </c>
       <c r="B7" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745308</v>
+        <v>745337</v>
       </c>
       <c r="R7" t="n">
-        <v>7103303</v>
+        <v>7103251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126055038</v>
+        <v>126055037</v>
       </c>
       <c r="B8" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745343</v>
+        <v>745308</v>
       </c>
       <c r="R8" t="n">
-        <v>7103338</v>
+        <v>7103303</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1332,12 +1337,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126055042</v>
+        <v>126055038</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>98364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745337</v>
+        <v>745343</v>
       </c>
       <c r="R9" t="n">
-        <v>7103251</v>
+        <v>7103338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1429,17 +1434,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26484-2025 artfynd.xlsx
+++ b/artfynd/A 26484-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126055046</v>
       </c>
       <c r="B2" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126055035</v>
       </c>
       <c r="B3" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126055045</v>
       </c>
       <c r="B5" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126055043</v>
       </c>
       <c r="B6" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126055042</v>
+        <v>126055037</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745337</v>
+        <v>745308</v>
       </c>
       <c r="R7" t="n">
-        <v>7103251</v>
+        <v>7103303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126055037</v>
+        <v>126055038</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745308</v>
+        <v>745343</v>
       </c>
       <c r="R8" t="n">
-        <v>7103303</v>
+        <v>7103338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,12 +1332,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126055038</v>
+        <v>126055042</v>
       </c>
       <c r="B9" t="n">
-        <v>98364</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745343</v>
+        <v>745337</v>
       </c>
       <c r="R9" t="n">
-        <v>7103338</v>
+        <v>7103251</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,12 +1429,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26484-2025 artfynd.xlsx
+++ b/artfynd/A 26484-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126055046</v>
       </c>
       <c r="B2" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126055035</v>
       </c>
       <c r="B3" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126055041</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126055045</v>
       </c>
       <c r="B5" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126055043</v>
       </c>
       <c r="B6" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>126055037</v>
       </c>
       <c r="B7" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>126055038</v>
       </c>
       <c r="B8" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126055042</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26484-2025 artfynd.xlsx
+++ b/artfynd/A 26484-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126055046</v>
       </c>
       <c r="B2" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126055045</v>
       </c>
       <c r="B5" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126055043</v>
       </c>
       <c r="B6" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126055037</v>
+        <v>126055042</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745308</v>
+        <v>745337</v>
       </c>
       <c r="R7" t="n">
-        <v>7103303</v>
+        <v>7103251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126055038</v>
+        <v>126055037</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745343</v>
+        <v>745308</v>
       </c>
       <c r="R8" t="n">
-        <v>7103338</v>
+        <v>7103303</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1332,12 +1337,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126055042</v>
+        <v>126055038</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745337</v>
+        <v>745343</v>
       </c>
       <c r="R9" t="n">
-        <v>7103251</v>
+        <v>7103338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1429,17 +1434,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26484-2025 artfynd.xlsx
+++ b/artfynd/A 26484-2025 artfynd.xlsx
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126055042</v>
+        <v>126055037</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745337</v>
+        <v>745308</v>
       </c>
       <c r="R7" t="n">
-        <v>7103251</v>
+        <v>7103303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126055037</v>
+        <v>126055038</v>
       </c>
       <c r="B8" t="n">
         <v>98373</v>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745308</v>
+        <v>745343</v>
       </c>
       <c r="R8" t="n">
-        <v>7103303</v>
+        <v>7103338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,12 +1332,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126055038</v>
+        <v>126055042</v>
       </c>
       <c r="B9" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745343</v>
+        <v>745337</v>
       </c>
       <c r="R9" t="n">
-        <v>7103338</v>
+        <v>7103251</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,12 +1429,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26484-2025 artfynd.xlsx
+++ b/artfynd/A 26484-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126055046</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126055035</v>
       </c>
       <c r="B3" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126055041</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126055045</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126055043</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126055037</v>
+        <v>126055042</v>
       </c>
       <c r="B7" t="n">
-        <v>98373</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745308</v>
+        <v>745337</v>
       </c>
       <c r="R7" t="n">
-        <v>7103303</v>
+        <v>7103251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126055038</v>
+        <v>126055037</v>
       </c>
       <c r="B8" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745343</v>
+        <v>745308</v>
       </c>
       <c r="R8" t="n">
-        <v>7103338</v>
+        <v>7103303</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1332,12 +1337,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126055042</v>
+        <v>126055038</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>98382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745337</v>
+        <v>745343</v>
       </c>
       <c r="R9" t="n">
-        <v>7103251</v>
+        <v>7103338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1429,17 +1434,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
